--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-workflowExtension.xlsx
+++ b/docs/StructureDefinition-workflowExtension.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -289,14 +289,21 @@
     <t>Extension.extension</t>
   </si>
   <si>
-    <t>2</t>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -321,6 +328,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>Reference genome build.</t>
+  </si>
+  <si>
     <t>Extension.extension:genomeBuild.id</t>
   </si>
   <si>
@@ -331,6 +341,9 @@
   </si>
   <si>
     <t>Extension.extension.extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>Extension.extension:genomeBuild.url</t>
@@ -393,7 +406,7 @@
     <t>pipeline</t>
   </si>
   <si>
-    <t>No description</t>
+    <t>Pipeline used to produce the analysis.</t>
   </si>
   <si>
     <t>Extension.extension:pipeline.id</t>
@@ -740,7 +753,7 @@
     <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.26171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1103,11 +1116,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>77</v>
@@ -1125,12 +1138,14 @@
         <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>20</v>
@@ -1167,19 +1182,19 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1194,31 +1209,31 @@
         <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>20</v>
@@ -1233,7 +1248,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1284,7 +1299,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1304,10 +1319,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1407,10 +1422,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1439,7 +1454,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1478,19 +1493,19 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1510,10 +1525,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1536,16 +1551,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1553,7 +1568,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1595,7 +1610,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>82</v>
@@ -1610,15 +1625,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1641,13 +1656,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1674,11 +1689,11 @@
         <v>20</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>20</v>
@@ -1696,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1708,34 +1723,34 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -1750,7 +1765,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1801,7 +1816,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -1821,10 +1836,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1924,10 +1939,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1956,7 +1971,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1995,19 +2010,19 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2027,10 +2042,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2053,16 +2068,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2070,7 +2085,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2112,7 +2127,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -2127,15 +2142,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2161,10 +2176,10 @@
         <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2215,7 +2230,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2227,18 +2242,18 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2261,16 +2276,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2320,7 +2335,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -2335,15 +2350,15 @@
         <v>20</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2366,13 +2381,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2423,7 +2438,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2435,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
